--- a/backtest_runs/20260410_193731/by_symbol/FTSM/FTSM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FTSM/FTSM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100000</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>100000</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100000</v>
@@ -1185,7 +1185,7 @@
         <v>-7705.949999999996</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>120664</v>
@@ -1231,7 +1231,7 @@
         <v>-11193.00000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>109471</v>
@@ -1277,7 +1277,7 @@
         <v>-10202.84999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>99268.15000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-8179.500000000009</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>91088.64999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-12140.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>116574.25</v>
@@ -1645,7 +1645,7 @@
         <v>-2970.44999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>117564.4</v>
